--- a/docs/assets/202502_introSeries/data.xlsx
+++ b/docs/assets/202502_introSeries/data.xlsx
@@ -31407,8 +31407,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008A3DEA72C7889E40A6136363ABA1595A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="92f77b6875f2886d5763f599cbbbcc9f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3564ae3e-d959-4e20-bbbb-a185964b0db0" xmlns:ns3="43e3a3bd-a9a1-4304-9d57-cce0294d83e0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e1a052b3e7b3880a215095df53a19c3" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008A3DEA72C7889E40A6136363ABA1595A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba2a410e037698a0bf83fca3a9e12443">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3564ae3e-d959-4e20-bbbb-a185964b0db0" xmlns:ns3="43e3a3bd-a9a1-4304-9d57-cce0294d83e0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb687c4d63d979fa55b7a9bd18c4282e" ns2:_="" ns3:_="">
     <xsd:import namespace="3564ae3e-d959-4e20-bbbb-a185964b0db0"/>
     <xsd:import namespace="43e3a3bd-a9a1-4304-9d57-cce0294d83e0"/>
     <xsd:element name="properties">
@@ -31622,7 +31622,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41C4CA84-C88E-42CA-996D-B3FEC4086C40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A33E63C6-7FAD-4087-87CB-327E2766BB61}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
